--- a/18/food/2026-01-19-sm.xlsx
+++ b/18/food/2026-01-19-sm.xlsx
@@ -860,7 +860,7 @@
       </c>
       <c r="J1" s="11" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>19.01.2026</t>
         </is>
       </c>
     </row>
